--- a/data/trans_orig/P21B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21B-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según tipo de servicio de urgencias utilizado en 2007</t>
+          <t>Población según a dónde pertenecía el último servicio de urgencias que utilizó en los últimos 12 meses en 2007 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5755</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6439</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -846,97 +846,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1913</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>851</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4627</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3983</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -959,97 +959,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1913</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46204</t>
+          <t>45440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51183</t>
+          <t>51728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>62838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92718</t>
+          <t>92109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>64954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84808</t>
+          <t>84595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84020</t>
+          <t>83975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104901</t>
+          <t>103835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153837</t>
+          <t>154190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182759</t>
+          <t>183639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -1415,97 +1415,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>42950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69476</t>
+          <t>69491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89659</t>
+          <t>88214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122345</t>
+          <t>121053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142048</t>
+          <t>141176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179781</t>
+          <t>181355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113209</t>
+          <t>112871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139026</t>
+          <t>139573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154746</t>
+          <t>155455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187097</t>
+          <t>188106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>277426</t>
+          <t>276439</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317397</t>
+          <t>318630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -2097,97 +2097,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4496</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3725</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3748</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22190</t>
+          <t>23390</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27256</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31936</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53874</t>
+          <t>53698</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>47700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73502</t>
+          <t>73606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83432</t>
+          <t>83023</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103211</t>
+          <t>102770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112767</t>
+          <t>112825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>137085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>203135</t>
+          <t>204235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>232815</t>
+          <t>234526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>836</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>845</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19706</t>
+          <t>19793</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38005</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31051</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>55677</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55538</t>
+          <t>55648</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86745</t>
+          <t>84053</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>88486</t>
+          <t>87893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108795</t>
+          <t>109073</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162673</t>
+          <t>162192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187777</t>
+          <t>187402</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>257701</t>
+          <t>258344</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>289185</t>
+          <t>289276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>23840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35854</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22318</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33892</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>117606</t>
+          <t>117442</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>159123</t>
+          <t>159373</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>201395</t>
+          <t>205256</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>256348</t>
+          <t>256541</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>336815</t>
+          <t>335936</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>399940</t>
+          <t>400741</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>372502</t>
+          <t>372893</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>414546</t>
+          <t>416360</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>538971</t>
+          <t>539307</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>595206</t>
+          <t>590802</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>927786</t>
+          <t>931911</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>994856</t>
+          <t>998117</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según tipo de servicio de urgencias utilizado en 2012</t>
+          <t>Población según a dónde pertenecía el último servicio de urgencias que utilizó en los últimos 12 meses en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,62 +4410,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4523</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4627</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -4488,97 +4488,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5234</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1039</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4232</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34929</t>
+          <t>35291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57279</t>
+          <t>57427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>44867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69489</t>
+          <t>70335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85833</t>
+          <t>86110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119175</t>
+          <t>119213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79182</t>
+          <t>78276</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102495</t>
+          <t>101708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120105</t>
+          <t>120064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>146304</t>
+          <t>145986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,47 +4877,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>62,08%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>75,49%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>224891</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>207941</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>241665</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>67,17%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>62,11%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>75,65%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>224891</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>207007</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>241709</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>67,17%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>61,83%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -5057,97 +5057,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5170,97 +5170,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93513</t>
+          <t>93880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125816</t>
+          <t>125363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108425</t>
+          <t>109778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143845</t>
+          <t>146078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213116</t>
+          <t>211642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260397</t>
+          <t>260755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99662</t>
+          <t>99209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131218</t>
+          <t>129206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154479</t>
+          <t>152140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189922</t>
+          <t>188370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263076</t>
+          <t>263110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310005</t>
+          <t>311469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,62 +5774,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5089</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6136</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,42 +5872,42 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7140</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15599</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7140</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>15730</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44623</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>72261</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58204</t>
+          <t>56795</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>86884</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109220</t>
+          <t>109846</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148789</t>
+          <t>149274</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>104474</t>
+          <t>103334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>131285</t>
+          <t>130991</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160680</t>
+          <t>159901</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>190511</t>
+          <t>192191</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>274879</t>
+          <t>273309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>314732</t>
+          <t>314665</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -6421,97 +6421,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>19579</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>24665</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45527</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>39125</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63986</t>
+          <t>65220</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>68823</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102371</t>
+          <t>100652</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102425</t>
+          <t>102383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124774</t>
+          <t>124561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>145821</t>
+          <t>144985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>173793</t>
+          <t>172278</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>255738</t>
+          <t>256978</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>291085</t>
+          <t>291327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,62 +7138,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2069</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>8033</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26365</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30955</t>
+          <t>31404</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>22518</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>24939</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19010</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>43496</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>221581</t>
+          <t>222008</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>271973</t>
+          <t>274946</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>272568</t>
+          <t>278864</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>331010</t>
+          <t>335741</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>512491</t>
+          <t>513232</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>589288</t>
+          <t>590239</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>412831</t>
+          <t>412287</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>463905</t>
+          <t>465060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>614511</t>
+          <t>608631</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>678360</t>
+          <t>670044</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1036286</t>
+          <t>1041013</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1119716</t>
+          <t>1117963</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,51%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según tipo de servicio de urgencias utilizado en 2016</t>
+          <t>Población según a dónde pertenecía el último servicio de urgencias que utilizó en los últimos 12 meses en 2016 (tasa de respuesta: 98,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,62 +8052,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4083</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4062</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24276</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43736</t>
+          <t>44649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35166</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57670</t>
+          <t>56830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64329</t>
+          <t>67374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94508</t>
+          <t>94834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56115</t>
+          <t>56528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75748</t>
+          <t>75332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74218</t>
+          <t>74222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96256</t>
+          <t>96285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135375</t>
+          <t>136178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167444</t>
+          <t>164656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24754</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>32103</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61623</t>
+          <t>62184</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54370</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82641</t>
+          <t>85320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100090</t>
+          <t>101567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137369</t>
+          <t>138126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92065</t>
+          <t>90539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118960</t>
+          <t>116711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119939</t>
+          <t>117072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148525</t>
+          <t>146302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217821</t>
+          <t>218317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>255806</t>
+          <t>254602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -9381,97 +9381,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16833</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26664</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47257</t>
+          <t>46321</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41751</t>
+          <t>41122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65836</t>
+          <t>66969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73563</t>
+          <t>73222</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106219</t>
+          <t>106625</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72792</t>
+          <t>72345</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93867</t>
+          <t>95062</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74183</t>
+          <t>73060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98292</t>
+          <t>99028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>153589</t>
+          <t>151473</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>186150</t>
+          <t>186916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13751</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23277</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31193</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24649</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>30801</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27807</t>
+          <t>26570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>49701</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47215</t>
+          <t>46382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74425</t>
+          <t>75688</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105913</t>
+          <t>105471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126650</t>
+          <t>125618</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167270</t>
+          <t>169556</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>195810</t>
+          <t>197333</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>281111</t>
+          <t>280948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>315910</t>
+          <t>316690</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41495</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27976</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54163</t>
+          <t>53905</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>17612</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>39929</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>35656</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36842</t>
+          <t>36339</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>68198</t>
+          <t>65669</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>120748</t>
+          <t>119692</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>163698</t>
+          <t>162131</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>183628</t>
+          <t>180694</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>231564</t>
+          <t>231997</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>315464</t>
+          <t>314605</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>381831</t>
+          <t>381233</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>347159</t>
+          <t>344350</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>392587</t>
+          <t>393178</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>462421</t>
+          <t>459659</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>514228</t>
+          <t>515403</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>820824</t>
+          <t>825972</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>893616</t>
+          <t>895789</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,87%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según tipo de servicio de urgencias utilizado en 2023</t>
+          <t>Población según a dónde pertenecía el último servicio de urgencias que utilizó en los últimos 12 meses en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,97 +11659,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1632</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1667</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5713</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1632</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6186</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1632</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6425</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>21961</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>908</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21381</t>
+          <t>21872</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>18969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>21514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36262</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>43624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68465</t>
+          <t>68833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79370</t>
+          <t>81370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102212</t>
+          <t>103256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99498</t>
+          <t>98783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116354</t>
+          <t>115948</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185635</t>
+          <t>186911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212432</t>
+          <t>214835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19788</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45007</t>
+          <t>44537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79642</t>
+          <t>79999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48238</t>
+          <t>47062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70809</t>
+          <t>70316</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100109</t>
+          <t>101533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140244</t>
+          <t>141535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121878</t>
+          <t>122857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158029</t>
+          <t>158127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151322</t>
+          <t>150420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175283</t>
+          <t>174733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283620</t>
+          <t>280658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325141</t>
+          <t>324094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -13023,97 +13023,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5847</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1399</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5528</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5558</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5627</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26677</t>
+          <t>25989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27845</t>
+          <t>28669</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34949</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>31655</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89622</t>
+          <t>90854</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109975</t>
+          <t>106419</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94721</t>
+          <t>94476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116382</t>
+          <t>116706</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254788</t>
+          <t>251935</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>373082</t>
+          <t>372143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>366491</t>
+          <t>367389</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498381</t>
+          <t>499989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30700</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26257</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>22598</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44720</t>
+          <t>44935</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>12468</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>32811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32599</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55261</t>
+          <t>53131</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50466</t>
+          <t>49277</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80622</t>
+          <t>77488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>134342</t>
+          <t>134509</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160461</t>
+          <t>160417</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>191748</t>
+          <t>192825</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>218736</t>
+          <t>219205</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>334154</t>
+          <t>338031</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>371796</t>
+          <t>373268</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15954</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29661</t>
+          <t>30288</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41248</t>
+          <t>42880</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64786</t>
+          <t>65136</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49467</t>
+          <t>51023</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52993</t>
+          <t>53593</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45804</t>
+          <t>47461</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>92566</t>
+          <t>92606</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>106600</t>
+          <t>106625</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>154697</t>
+          <t>153745</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>89455</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>218688</t>
+          <t>219655</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>184271</t>
+          <t>192739</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>351906</t>
+          <t>347886</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>459694</t>
+          <t>459577</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>513357</t>
+          <t>513582</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>739707</t>
+          <t>737411</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>920660</t>
+          <t>917755</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1222750</t>
+          <t>1231457</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1443166</t>
+          <t>1437302</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21B-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26715</t>
+          <t>26953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>46467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31874</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51728</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62838</t>
+          <t>63328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92109</t>
+          <t>91238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64954</t>
+          <t>65183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84595</t>
+          <t>84231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83975</t>
+          <t>82311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103835</t>
+          <t>103329</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154190</t>
+          <t>155295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183639</t>
+          <t>183253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>13512</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42950</t>
+          <t>42687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69491</t>
+          <t>67522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88214</t>
+          <t>90570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121053</t>
+          <t>123086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141176</t>
+          <t>141363</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181355</t>
+          <t>185320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112871</t>
+          <t>114742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139573</t>
+          <t>140275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155455</t>
+          <t>154253</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188106</t>
+          <t>187022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276439</t>
+          <t>275409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318630</t>
+          <t>318780</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,89%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>23598</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27187</t>
+          <t>26842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53698</t>
+          <t>51997</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47700</t>
+          <t>47113</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73606</t>
+          <t>74396</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83023</t>
+          <t>84493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>102971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112825</t>
+          <t>114974</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>137085</t>
+          <t>138100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204235</t>
+          <t>202988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>234526</t>
+          <t>235146</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>15897</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>906</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19793</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39386</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55677</t>
+          <t>53392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55648</t>
+          <t>55734</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84053</t>
+          <t>85069</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87893</t>
+          <t>87336</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109073</t>
+          <t>108898</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162192</t>
+          <t>162051</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187402</t>
+          <t>187909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>258344</t>
+          <t>258767</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>289276</t>
+          <t>290002</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>35961</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>34411</t>
+          <t>35058</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>117442</t>
+          <t>118088</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>159373</t>
+          <t>157516</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>205256</t>
+          <t>204759</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>256541</t>
+          <t>257856</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>335936</t>
+          <t>336231</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>400741</t>
+          <t>397632</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>372893</t>
+          <t>373898</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>416360</t>
+          <t>417553</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>539307</t>
+          <t>538589</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>590802</t>
+          <t>592110</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>931911</t>
+          <t>932002</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>998117</t>
+          <t>998218</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>34576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57427</t>
+          <t>56780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70335</t>
+          <t>69130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86110</t>
+          <t>85221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119213</t>
+          <t>118686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78276</t>
+          <t>79089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101708</t>
+          <t>102900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120064</t>
+          <t>121190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145986</t>
+          <t>147058</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207941</t>
+          <t>207898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>241665</t>
+          <t>242305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93880</t>
+          <t>93660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125363</t>
+          <t>125926</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109778</t>
+          <t>107421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146078</t>
+          <t>144050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211642</t>
+          <t>212866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260755</t>
+          <t>261356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99209</t>
+          <t>98685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129206</t>
+          <t>130661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152140</t>
+          <t>154235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188370</t>
+          <t>189690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263110</t>
+          <t>262476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>311469</t>
+          <t>310584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,8%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18559</t>
+          <t>18732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45588</t>
+          <t>44802</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72261</t>
+          <t>70949</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56795</t>
+          <t>57611</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86884</t>
+          <t>86295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109846</t>
+          <t>111133</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149274</t>
+          <t>150531</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103334</t>
+          <t>104368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130991</t>
+          <t>132020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159901</t>
+          <t>160271</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>192191</t>
+          <t>190455</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>273309</t>
+          <t>272253</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>314665</t>
+          <t>314633</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19579</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24665</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>44410</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39125</t>
+          <t>37307</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>63078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68823</t>
+          <t>68292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100652</t>
+          <t>100044</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102383</t>
+          <t>103251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124561</t>
+          <t>124666</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>144985</t>
+          <t>145338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>172278</t>
+          <t>172963</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>256978</t>
+          <t>254899</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>291327</t>
+          <t>292011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>942</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26706</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>31519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22518</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24939</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40350</t>
+          <t>39925</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>222008</t>
+          <t>220041</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>274946</t>
+          <t>274121</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>278864</t>
+          <t>274017</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>335741</t>
+          <t>335922</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>513232</t>
+          <t>514448</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>590239</t>
+          <t>591511</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>412287</t>
+          <t>411901</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>465060</t>
+          <t>465716</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>608631</t>
+          <t>609267</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>670044</t>
+          <t>672520</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1041013</t>
+          <t>1039157</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1117963</t>
+          <t>1120089</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25511</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44649</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35142</t>
+          <t>35052</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56830</t>
+          <t>56571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67374</t>
+          <t>65392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94834</t>
+          <t>93487</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56528</t>
+          <t>56140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75332</t>
+          <t>75170</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74222</t>
+          <t>73191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96285</t>
+          <t>96301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136178</t>
+          <t>136859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>164656</t>
+          <t>166189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>24792</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32103</t>
+          <t>34428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>37018</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62184</t>
+          <t>61404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>55695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85320</t>
+          <t>83845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101567</t>
+          <t>100117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138126</t>
+          <t>137651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90539</t>
+          <t>90575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116711</t>
+          <t>117678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117072</t>
+          <t>117837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146302</t>
+          <t>146973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218317</t>
+          <t>216149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254602</t>
+          <t>256636</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>16889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11572</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46321</t>
+          <t>47976</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41122</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66969</t>
+          <t>66974</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73222</t>
+          <t>73830</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106625</t>
+          <t>106476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72345</t>
+          <t>71197</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95062</t>
+          <t>93895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73060</t>
+          <t>73307</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99028</t>
+          <t>98297</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151473</t>
+          <t>151300</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>186916</t>
+          <t>185853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>32272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>18055</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>23413</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30801</t>
+          <t>31325</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49701</t>
+          <t>50577</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46382</t>
+          <t>47609</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>75688</t>
+          <t>76755</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105471</t>
+          <t>104222</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>125618</t>
+          <t>126171</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169556</t>
+          <t>168652</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>197333</t>
+          <t>196936</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280948</t>
+          <t>279356</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>316690</t>
+          <t>316146</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>18888</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41040</t>
+          <t>42604</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27817</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53905</t>
+          <t>54235</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>38384</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35656</t>
+          <t>35022</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36339</t>
+          <t>37157</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>65669</t>
+          <t>66057</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>119692</t>
+          <t>121359</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>162131</t>
+          <t>163709</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>180694</t>
+          <t>179602</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>231997</t>
+          <t>229890</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>314605</t>
+          <t>313682</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>381233</t>
+          <t>377832</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>344350</t>
+          <t>345159</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>393178</t>
+          <t>391654</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>459659</t>
+          <t>461200</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>515403</t>
+          <t>515948</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>825972</t>
+          <t>825511</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>895789</t>
+          <t>896401</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>25760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>26301</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27750</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38258</t>
+          <t>39537</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28341</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>21491</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37409</t>
+          <t>37809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>56091</t>
+          <t>58269</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>46934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68833</t>
+          <t>71814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92533</t>
+          <t>99952</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81370</t>
+          <t>86947</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103256</t>
+          <t>109868</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>108117</t>
+          <t>117820</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98783</t>
+          <t>108522</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115948</t>
+          <t>125622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>200651</t>
+          <t>217771</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186911</t>
+          <t>201055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>214835</t>
+          <t>231301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,15%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128631</t>
+          <t>138529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128631</t>
+          <t>138529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128631</t>
+          <t>138529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>143094</t>
+          <t>153684</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143094</t>
+          <t>153684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143094</t>
+          <t>153684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>271725</t>
+          <t>292213</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>271725</t>
+          <t>292213</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>271725</t>
+          <t>292213</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>732</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,17 +12632,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19684</t>
+          <t>21595</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60037</t>
+          <t>60763</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44537</t>
+          <t>44223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79999</t>
+          <t>78266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59530</t>
+          <t>65226</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47062</t>
+          <t>53885</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70316</t>
+          <t>78288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>119567</t>
+          <t>125989</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>107905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141535</t>
+          <t>148833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>141239</t>
+          <t>160367</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122857</t>
+          <t>142165</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158127</t>
+          <t>175989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>163258</t>
+          <t>180822</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150420</t>
+          <t>166742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174733</t>
+          <t>194354</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>304497</t>
+          <t>341189</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280658</t>
+          <t>319693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324094</t>
+          <t>360394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>213681</t>
+          <t>234367</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>213681</t>
+          <t>234367</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>213681</t>
+          <t>234367</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>236136</t>
+          <t>260706</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>236136</t>
+          <t>260706</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>236136</t>
+          <t>260706</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>449817</t>
+          <t>495073</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>449817</t>
+          <t>495073</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>449817</t>
+          <t>495073</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>10399</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21629</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25989</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>16758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28669</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>21616</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35676</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31655</t>
+          <t>37302</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39189</t>
+          <t>44783</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90854</t>
+          <t>57013</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>61006</t>
+          <t>70431</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>56990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106419</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>105863</t>
+          <t>112294</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94476</t>
+          <t>99627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116706</t>
+          <t>123971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>329629</t>
+          <t>148312</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251935</t>
+          <t>134923</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>372143</t>
+          <t>159891</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>435492</t>
+          <t>260607</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367389</t>
+          <t>243057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>499989</t>
+          <t>278501</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>139569</t>
+          <t>152799</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>139569</t>
+          <t>152799</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>139569</t>
+          <t>152799</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>389764</t>
+          <t>217971</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>389764</t>
+          <t>217971</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>389764</t>
+          <t>217971</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>529333</t>
+          <t>370771</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>529333</t>
+          <t>370771</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>529333</t>
+          <t>370771</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13770,22 +13770,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>816</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>21173</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24148</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>32211</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22598</t>
+          <t>23892</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44935</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>32959</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>32956</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53131</t>
+          <t>55219</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>62159</t>
+          <t>64568</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>50808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>77488</t>
+          <t>80999</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>148383</t>
+          <t>158461</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>134509</t>
+          <t>144281</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160417</t>
+          <t>170653</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>206194</t>
+          <t>228755</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>192825</t>
+          <t>214201</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>219205</t>
+          <t>241474</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>354577</t>
+          <t>387216</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>338031</t>
+          <t>368558</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>373268</t>
+          <t>404595</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>194335</t>
+          <t>206766</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>194335</t>
+          <t>206766</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>194335</t>
+          <t>206766</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>277492</t>
+          <t>302368</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>277492</t>
+          <t>302368</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>277492</t>
+          <t>302368</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>471827</t>
+          <t>509135</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>471827</t>
+          <t>509135</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>471827</t>
+          <t>509135</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,22 +14382,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15468</t>
+          <t>17412</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>13378</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30288</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42880</t>
+          <t>44384</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>53221</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30999</t>
+          <t>40316</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65136</t>
+          <t>68076</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>33956</t>
+          <t>37368</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51023</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>37602</t>
+          <t>40897</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53593</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>71558</t>
+          <t>78265</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47461</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>92606</t>
+          <t>101484</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>129895</t>
+          <t>137862</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>106625</t>
+          <t>114994</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>153745</t>
+          <t>165697</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>168928</t>
+          <t>181395</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>89455</t>
+          <t>158642</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>219655</t>
+          <t>203915</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>298822</t>
+          <t>319257</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>192739</t>
+          <t>284283</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>347886</t>
+          <t>352592</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>488018</t>
+          <t>531074</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>459577</t>
+          <t>501742</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>513582</t>
+          <t>556910</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>807198</t>
+          <t>675708</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>737411</t>
+          <t>652075</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>917755</t>
+          <t>701278</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1295216</t>
+          <t>1206783</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1231457</t>
+          <t>1168277</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1437302</t>
+          <t>1243535</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>676216</t>
+          <t>732461</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>676216</t>
+          <t>732461</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>676216</t>
+          <t>732461</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1046486</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1046486</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1046486</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1722702</t>
+          <t>1667191</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1722702</t>
+          <t>1667191</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1722702</t>
+          <t>1667191</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
